--- a/report/downloads/reports/网点变化对比报告_20260727.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260727.xlsx
@@ -10,7 +10,7 @@
     <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="新增网点（30家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（44家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="减少网点（24家）" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="变更明细（20条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -478,7 +478,7 @@
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -719,23 +719,23 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>-20</v>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-100.0%</t>
+      <c r="C12" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -875,14 +875,14 @@
         <v>8632</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8618</v>
+        <v>8638</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>-14</v>
+        <v>6</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.1%</t>
         </is>
       </c>
     </row>
@@ -6332,339 +6332,339 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="4" t="inlineStr">
+      <c r="A259" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B259" s="4" t="inlineStr">
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D259" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E259" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D260" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E260" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D261" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E261" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D262" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E262" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D263" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E263" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D264" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E264" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D265" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E265" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D266" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E266" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D267" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E267" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
         <is>
           <t>浙江</t>
         </is>
       </c>
-      <c r="C259" s="4" t="n">
+      <c r="C268" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D259" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E259" s="4" t="n">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="4" t="inlineStr">
+      <c r="D268" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E268" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B260" s="4" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C260" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D260" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E260" s="4" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="4" t="inlineStr">
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D269" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E269" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B261" s="4" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="C261" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D261" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E261" s="4" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="4" t="inlineStr">
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D270" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E270" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B262" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C262" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D262" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E262" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="4" t="inlineStr">
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D271" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E271" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B263" s="4" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C263" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D263" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E263" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="4" t="inlineStr">
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D272" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E272" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B264" s="4" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C264" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D264" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E264" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="4" t="inlineStr">
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D273" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E273" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B265" s="4" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C265" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D265" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E265" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B266" s="4" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C266" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D266" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E266" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B267" s="4" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C267" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D267" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E267" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B268" s="4" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C268" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D268" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E268" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B269" s="4" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="C269" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D269" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E269" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B270" s="4" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C270" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D270" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E270" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B271" s="4" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C271" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D271" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E271" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B272" s="4" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="C272" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D272" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E272" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B273" s="4" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="C273" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D273" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E273" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B274" s="4" t="inlineStr">
+      <c r="B274" s="3" t="inlineStr">
         <is>
           <t>陕西</t>
         </is>
       </c>
-      <c r="C274" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D274" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E274" s="4" t="n">
-        <v>-1</v>
+      <c r="C274" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D274" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>小米汽车广东省广州市花都区建设北路</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>龙溪大道502号自编1</t>
+          <t>广东省广州市花都区建设北路223号</t>
         </is>
       </c>
     </row>
@@ -10503,7 +10503,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市花都区建设北路</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市花都区建设北路223号</t>
+          <t>龙溪大道502号自编1</t>
         </is>
       </c>
     </row>
@@ -10938,7 +10938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11194,970 +11194,430 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>意特汽车商业（上海）有限公司</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>恒通东路69号101单元 龙盛福新汇 上海 上海</t>
+          <t>广东省深圳市广东省深圳市福田区岗厦一路深圳卓悦中心西区L1层CD574号展位</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>昆明乐骏汽车销售服务有限公司</t>
+          <t>湛江特斯拉中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>昆明市</t>
+          <t>湛江市</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>滇池度假区滇池路1103号平安大厦B座1层 平安大厦 昆明市 滇池度假区</t>
+          <t>广东省湛江市瑞云北路101号之十六(粤西国际车城内，南亚郦都小区对面)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>北京骏东汽车销售服务有限公司</t>
+          <t>福州万象城体验店</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>福州市</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>金宝街 金宝大厦一层 北京 东城区</t>
+          <t>福建省福州市鼓楼区洪山园路5号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>成都骏意汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>成都市</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>成都市高新区火车南站西路 法拉利 成都市 中国</t>
+          <t>深圳市</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>安徽鸿粤鸿超汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>合肥市</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>花亭湖路与齐云山路交叉口 安徽鸿粤鸿超汽车销售服务有限公司 合肥 蜀山区</t>
+          <t>深圳市福田区</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>青岛恒骏汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•赤峰桥北物流园</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>青岛市</t>
+          <t>赤峰市</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>青岛市市南区东海西路1号1号楼丙户 青岛市 市南区</t>
+          <t>内蒙古自治区赤峰市红山区桥北物流园区火花北路111号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>广东骏佳汽车服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>广州市</t>
+          <t>鄂尔多斯市</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>天河区珠江新城清风街1-48号 新世界广场首层 Guangzhou</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>骏佳行汽车服务（深圳）有限公司</t>
+          <t>鸿蒙智行尚界用户中心•吉林大街</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>吉林市</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>中心路1号 深圳湾壹号北区2栋 Shenzhen Nanshan District</t>
+          <t>吉林高新区吉林大街32号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>南京瑞骏汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>南京市</t>
+          <t>长春市</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>长江路100号 长江会 南京 玄武</t>
+          <t>吉林省长春市高新区硅谷大街5555号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>苏州意骏汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>眉山市</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>苏州工业园区思安街99号协鑫广场西侧1F Suzhou</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-2层</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>郑州悦骏汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>郑州市</t>
+          <t>芜湖市</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>如意西路 中国平煤神马集团 郑州 郑东新区</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>宁波骏意汽车服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•滨州渤海五路</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>宁波市</t>
+          <t>滨州市</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>中官新路 A号楼 Ningbo Jiangbei District</t>
+          <t>山东省滨州市滨城区黄河十五路渤海五路北200米路东</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>杭州骏意汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安鸿友汽车园</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>杭州市</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市南山路 杭州 上城区</t>
+          <t>广东省深圳市宝安区西乡中航飞翔工业园（G107西）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>温州骏意汽车服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>温州市</t>
+          <t>肇庆市</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>温州经济技术开发区滨海园区 3号4S店东侧 温州 中国</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>武汉骏东汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>武汉市</t>
+          <t>邵阳市</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>解放大道634号K11步行街 108-109 武汉 中国</t>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>长沙市骏马汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•齐齐哈尔永安南大街</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>长沙市</t>
+          <t>齐齐哈尔市</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>潇湘北路 圆泰长沙印 103-1 号 长沙市 中国</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>福建骏佳行汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>厦门市</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>环岛东路1821号 中航紫金广场商业街 厦门市 思明区</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>沈阳鸿粤鸿福汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>沈阳市</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>浑南区全运路 Shenyang China</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>重庆骏东汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>重庆两江新区新南路 龙湖晶郦馆A栋-1F-03b Chongqing New South St</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>西安市</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>深圳福田卓悦中心</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>深圳市</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>广东省深圳市广东省深圳市福田区岗厦一路深圳卓悦中心西区L1层CD574号展位</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>湛江特斯拉中心</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>湛江市</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>广东省湛江市瑞云北路101号之十六(粤西国际车城内，南亚郦都小区对面)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>福州万象城体验店</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>福州市</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>福建省福州市鼓楼区洪山园路5号</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•海南电动</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>深圳市福田区</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•贵州电动</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>深圳市</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•赤峰桥北物流园</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>赤峰市</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>内蒙古自治区赤峰市红山区桥北物流园区火花北路111号</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>鄂尔多斯市</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•吉林大街</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>吉林</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>吉林市</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>吉林高新区吉林大街32号</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>吉林</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>长春市</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>吉林省长春市高新区硅谷大街5555号</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>眉山市</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>芜湖市</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•滨州渤海五路</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>滨州市</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>山东省滨州市滨城区黄河十五路渤海五路北200米路东</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安鸿友汽车园</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>深圳市</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>广东省深圳市宝安区西乡中航飞翔工业园（G107西）</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>肇庆市</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>邵阳市</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•齐齐哈尔永安南大街</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>黑龙江</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>齐齐哈尔市</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>黑龙江省齐齐哈尔市龙沙区永安南大街135号</t>
         </is>
@@ -12225,17 +11685,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12245,29 +11705,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
+          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12277,7 +11737,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
+          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12289,17 +11749,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12309,7 +11769,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
+          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
         </is>
       </c>
     </row>
@@ -12321,17 +11781,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12341,7 +11801,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
+          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
         </is>
       </c>
     </row>
@@ -12353,17 +11813,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12373,7 +11833,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
+          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
         </is>
       </c>
     </row>
@@ -12385,17 +11845,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12405,7 +11865,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
+          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
@@ -12417,17 +11877,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12437,29 +11897,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳科盛路</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳科盛路</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12469,29 +11929,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>深圳市龙华区观湖街道鹭湖社区观盛五路9号A栋1F（临时营业） → 广东省深圳市龙华区观湖街道鹭湖社区观盛五路9号A栋1F</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12501,29 +11961,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
+          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳科盛路</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳科盛路</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12533,7 +11993,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙华区观湖街道鹭湖社区观盛五路9号A栋1F（临时营业） → 广东省深圳市龙华区观湖街道鹭湖社区观盛五路9号A栋1F</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
@@ -12545,17 +12005,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12565,7 +12025,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
+          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
         </is>
       </c>
     </row>
@@ -12577,17 +12037,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12597,7 +12057,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
+          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
         </is>
       </c>
     </row>
@@ -12609,17 +12069,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12629,7 +12089,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
+          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -12668,22 +12128,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>济南济西保时捷中心</t>
+          <t>华为授权体验店（融侨外滩壹号）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>济南保时捷中心</t>
+          <t>华为授权体验店（融侨外滩）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12700,22 +12160,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>济南济西保时捷中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>济南保时捷中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12737,17 +12197,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•无锡先锋中路</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•无锡先锋中路</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12769,17 +12229,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融侨外滩壹号）</t>
+          <t>鸿蒙智行授权用户中心•无锡先锋中路</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融侨外滩）</t>
+          <t>AITO授权用户中心•无锡先锋中路</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260727.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260727.xlsx
@@ -11006,7 +11006,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="33" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>连续在档 12 期</t>
+          <t>连续在档 12 期；本期存在高相似店名「兰州万象城体验店」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -11416,12 +11416,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>深圳市福田区</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>连续在档 4 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
+          <t>连续在档 5 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -11448,12 +11448,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>深圳市福田区</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>连续在档 5 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
+          <t>连续在档 4 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
         </is>
       </c>
     </row>
@@ -11485,7 +11485,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>连续在档 12 期</t>
+          <t>连续在档 12 期；本期存在高相似店名「鸿蒙智行授权用户中心•赤峰桥北物流园」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11517,7 +11517,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>连续在档 12 期</t>
+          <t>连续在档 12 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>连续在档 12 期</t>
+          <t>连续在档 12 期；本期存在高相似店名「AITO授权用户中心•长春硅谷大街」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11613,7 +11613,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>连续在档 1 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
+          <t>连续在档 1 期；历史有闪烁（疑似漏爬，关注下期是否回归）；本期存在高相似店名「鸿蒙智行智界用户中心•眉山眉州大道」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11645,7 +11645,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>连续在档 12 期</t>
+          <t>连续在档 12 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>连续在档 12 期</t>
+          <t>连续在档 12 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>连续在档 12 期</t>
+          <t>连续在档 12 期；本期存在高相似店名「AITO授权用户中心•深圳宝安鸿友汽车园」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>连续在档 12 期</t>
+          <t>连续在档 12 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>连续在档 12 期</t>
+          <t>连续在档 12 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
+          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
         </is>
       </c>
     </row>
@@ -11935,17 +11935,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11955,29 +11955,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
+          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳科盛路</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳科盛路</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
+          <t>深圳市龙华区观湖街道鹭湖社区观盛五路9号A栋1F（临时营业） → 广东省深圳市龙华区观湖街道鹭湖社区观盛五路9号A栋1F</t>
         </is>
       </c>
     </row>
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
+          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12051,29 +12051,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳科盛路</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳科盛路</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12083,29 +12083,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙华区观湖街道鹭湖社区观盛五路9号A栋1F（临时营业） → 广东省深圳市龙华区观湖街道鹭湖社区观盛五路9号A栋1F</t>
+          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
+          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
         </is>
       </c>
     </row>
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
+          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
+          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
         </is>
       </c>
     </row>
@@ -12191,17 +12191,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
         </is>
       </c>
     </row>
@@ -12228,12 +12228,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12243,29 +12243,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
+          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
         </is>
       </c>
     </row>
@@ -12287,17 +12287,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
+          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
         </is>
       </c>
     </row>
@@ -12346,22 +12346,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>济南济西保时捷中心</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>济南保时捷中心</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12383,17 +12383,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融侨外滩壹号）</t>
+          <t>鸿蒙智行授权用户中心•无锡先锋中路</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融侨外滩）</t>
+          <t>AITO授权用户中心•无锡先锋中路</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12410,22 +12410,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>济南济西保时捷中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>济南保时捷中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12447,17 +12447,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•无锡先锋中路</t>
+          <t>华为授权体验店（融侨外滩壹号）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•无锡先锋中路</t>
+          <t>华为授权体验店（融侨外滩）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260727.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260727.xlsx
@@ -10,8 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（27家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（24家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（21条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（15家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（19条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -851,17 +851,17 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1724</v>
+        <v>1460</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1711</v>
+        <v>1456</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-13</v>
+        <v>-4</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-0.3%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8635</v>
+        <v>8371</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8638</v>
+        <v>8383</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.1%</t>
         </is>
       </c>
     </row>
@@ -9426,17 +9426,17 @@
       </c>
       <c r="B406" s="4" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C406" s="4" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D406" s="4" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E406" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="407">
@@ -9447,143 +9447,143 @@
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C407" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D407" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E407" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="4" t="inlineStr">
+      <c r="A408" s="2" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B408" s="4" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C408" s="4" t="n">
-        <v>206</v>
-      </c>
-      <c r="D408" s="4" t="n">
-        <v>204</v>
-      </c>
-      <c r="E408" s="4" t="n">
-        <v>-2</v>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="D408" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="E408" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="4" t="inlineStr">
+      <c r="A409" s="2" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B409" s="4" t="inlineStr">
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D409" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E409" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D410" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E410" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="D411" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="E411" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
         <is>
           <t>四川</t>
         </is>
       </c>
-      <c r="C409" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="D409" s="4" t="n">
-        <v>92</v>
-      </c>
-      <c r="E409" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" s="4" t="inlineStr">
+      <c r="C412" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="D412" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="E412" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B410" s="4" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C410" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="D410" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="E410" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B411" s="4" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C411" s="4" t="n">
-        <v>106</v>
-      </c>
-      <c r="D411" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="E411" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B412" s="4" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C412" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="D412" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="E412" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B413" s="4" t="inlineStr">
-        <is>
-          <t>黑龙江</t>
-        </is>
-      </c>
-      <c r="C413" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D413" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="E413" s="4" t="n">
-        <v>-1</v>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D413" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E413" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="414">
@@ -9594,14 +9594,14 @@
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C414" s="2" t="n">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="D414" s="2" t="n">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="E414" s="2" t="n">
         <v>0</v>
@@ -9615,14 +9615,14 @@
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C415" s="2" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D415" s="2" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E415" s="2" t="n">
         <v>0</v>
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C416" s="2" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="D416" s="2" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="E416" s="2" t="n">
         <v>0</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C417" s="2" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D417" s="2" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E417" s="2" t="n">
         <v>0</v>
@@ -9678,14 +9678,14 @@
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C418" s="2" t="n">
-        <v>14</v>
+        <v>181</v>
       </c>
       <c r="D418" s="2" t="n">
-        <v>14</v>
+        <v>181</v>
       </c>
       <c r="E418" s="2" t="n">
         <v>0</v>
@@ -9699,14 +9699,14 @@
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C419" s="2" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D419" s="2" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E419" s="2" t="n">
         <v>0</v>
@@ -9720,14 +9720,14 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C420" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D420" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E420" s="2" t="n">
         <v>0</v>
@@ -9741,14 +9741,14 @@
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C421" s="2" t="n">
-        <v>26</v>
+        <v>124</v>
       </c>
       <c r="D421" s="2" t="n">
-        <v>26</v>
+        <v>124</v>
       </c>
       <c r="E421" s="2" t="n">
         <v>0</v>
@@ -9762,14 +9762,14 @@
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C422" s="2" t="n">
-        <v>143</v>
+        <v>39</v>
       </c>
       <c r="D422" s="2" t="n">
-        <v>143</v>
+        <v>39</v>
       </c>
       <c r="E422" s="2" t="n">
         <v>0</v>
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C423" s="2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D423" s="2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E423" s="2" t="n">
         <v>0</v>
@@ -9804,14 +9804,14 @@
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C424" s="2" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D424" s="2" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E424" s="2" t="n">
         <v>0</v>
@@ -9825,14 +9825,14 @@
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C425" s="2" t="n">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="D425" s="2" t="n">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="E425" s="2" t="n">
         <v>0</v>
@@ -9846,14 +9846,14 @@
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C426" s="2" t="n">
-        <v>152</v>
+        <v>11</v>
       </c>
       <c r="D426" s="2" t="n">
-        <v>152</v>
+        <v>11</v>
       </c>
       <c r="E426" s="2" t="n">
         <v>0</v>
@@ -9867,14 +9867,14 @@
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C427" s="2" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="D427" s="2" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="E427" s="2" t="n">
         <v>0</v>
@@ -9888,14 +9888,14 @@
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C428" s="2" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D428" s="2" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="E428" s="2" t="n">
         <v>0</v>
@@ -9913,10 +9913,10 @@
         </is>
       </c>
       <c r="C429" s="2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D429" s="2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E429" s="2" t="n">
         <v>0</v>
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="C430" s="2" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D430" s="2" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E430" s="2" t="n">
         <v>0</v>
@@ -9976,10 +9976,10 @@
         </is>
       </c>
       <c r="C432" s="2" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D432" s="2" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E432" s="2" t="n">
         <v>0</v>
@@ -9997,10 +9997,10 @@
         </is>
       </c>
       <c r="C433" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D433" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E433" s="2" t="n">
         <v>0</v>
@@ -10018,10 +10018,10 @@
         </is>
       </c>
       <c r="C434" s="2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D434" s="2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E434" s="2" t="n">
         <v>0</v>
@@ -10039,10 +10039,10 @@
         </is>
       </c>
       <c r="C435" s="2" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D435" s="2" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E435" s="2" t="n">
         <v>0</v>
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="C436" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D436" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E436" s="2" t="n">
         <v>0</v>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京朝阳区东坝万达</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -10274,12 +10274,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>东坝万达广场一层中庭</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>小米汽车北京朝阳区东坝万达</t>
+          <t>小米汽车北京市大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>东坝万达广场一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>小米汽车广东省广州市花都区建设北路</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>龙溪大道502号自编1</t>
+          <t>广东省广州市花都区建设北路223号</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市花都区建设北路</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市花都区建设北路223号</t>
+          <t>龙溪大道502号自编1</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -10998,7 +10998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11465,27 +11465,27 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•赤峰桥北物流园</t>
+          <t>鸿蒙智行尚界用户中心•吉林大街</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>赤峰市</t>
+          <t>吉林市</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>内蒙古自治区赤峰市红山区桥北物流园区火花北路111号</t>
+          <t>吉林高新区吉林大街32号</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>连续在档 12 期；本期存在高相似店名「鸿蒙智行授权用户中心•赤峰桥北物流园」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 12 期</t>
         </is>
       </c>
     </row>
@@ -11497,313 +11497,25 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行尚界用户中心•齐齐哈尔永安南大街</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>齐齐哈尔市</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼</t>
+          <t>黑龙江省齐齐哈尔市龙沙区永安南大街135号</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 12 期；本期同名店仍在档（地址写法变更，非关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•吉林大街</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>吉林</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>吉林市</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>吉林高新区吉林大街32号</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 12 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•长春硅谷大街</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>吉林</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>长春市</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>吉林省长春市高新区硅谷大街5555号</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 12 期；本期存在高相似店名「AITO授权用户中心•长春硅谷大街」（疑似改名/合并，非真实关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>眉山市</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 1 期；历史有闪烁（疑似漏爬，关注下期是否回归）；本期存在高相似店名「鸿蒙智行智界用户中心•眉山眉州大道」（疑似改名/合并，非真实关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>芜湖市</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 12 期；本期同名店仍在档（地址写法变更，非关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•滨州渤海五路</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>滨州市</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>山东省滨州市滨城区黄河十五路渤海五路北200米路东</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 12 期；本期同名店仍在档（地址写法变更，非关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安鸿友汽车园</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>深圳市</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>广东省深圳市宝安区西乡中航飞翔工业园（G107西）</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 12 期；本期存在高相似店名「AITO授权用户中心•深圳宝安鸿友汽车园」（疑似改名/合并，非真实关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>肇庆市</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 12 期；本期同名店仍在档（地址写法变更，非关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>邵阳市</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 12 期；本期同名店仍在档（地址写法变更，非关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•齐齐哈尔永安南大街</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>黑龙江</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>齐齐哈尔市</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>黑龙江省齐齐哈尔市龙沙区永安南大街135号</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>连续在档 12 期</t>
         </is>
@@ -11820,7 +11532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11871,17 +11583,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11891,7 +11603,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
+          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11615,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11923,7 +11635,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
+          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -11935,17 +11647,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11955,14 +11667,14 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
+          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -11972,12 +11684,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳科盛路</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳科盛路</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11987,29 +11699,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙华区观湖街道鹭湖社区观盛五路9号A栋1F（临时营业） → 广东省深圳市龙华区观湖街道鹭湖社区观盛五路9号A栋1F</t>
+          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12019,7 +11731,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
+          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
         </is>
       </c>
     </row>
@@ -12031,17 +11743,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12051,7 +11763,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
         </is>
       </c>
     </row>
@@ -12095,17 +11807,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12115,7 +11827,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
+          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
         </is>
       </c>
     </row>
@@ -12127,17 +11839,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12147,7 +11859,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
+          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
         </is>
       </c>
     </row>
@@ -12159,17 +11871,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12179,7 +11891,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
+          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
@@ -12191,17 +11903,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12211,7 +11923,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
+          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12223,17 +11935,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12243,29 +11955,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12275,7 +11987,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
+          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
         </is>
       </c>
     </row>
@@ -12287,59 +11999,59 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车常德大道销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
+          <t>小鹏汽车常德大道销售中心 → 小鹏汽车常德大道销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售服务中心</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>店名变更</t>
+          <t>地址变更</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 小鹏汽车常德大道销售服务中心</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
@@ -12351,17 +12063,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>华为授权体验店（融侨外滩壹号）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>华为授权体验店（融侨外滩）</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12378,22 +12090,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•无锡先锋中路</t>
+          <t>济南济西保时捷中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•无锡先锋中路</t>
+          <t>济南保时捷中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12410,22 +12122,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>济南济西保时捷中心</t>
+          <t>上海宝山龙湖天街城市展厅3号门</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>济南保时捷中心</t>
+          <t>上海宝山龙湖天街城市展厅1号门</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12435,101 +12147,37 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>地址归一前缀一致</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融侨外滩壹号）</t>
+          <t>小米汽车北京市朝阳区国贸销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融侨外滩）</t>
+          <t>小米汽车北京市朝阳区来广营销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>上海宝山龙湖天街城市展厅3号门</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>上海宝山龙湖天街城市展厅1号门</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>地址相似度 67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车北京市朝阳区国贸销售服务中心</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车北京市朝阳区来广营销售服务中心</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>店名相似度 80%</t>
         </is>

--- a/report/downloads/reports/网点变化对比报告_20260727.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260727.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（27家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（28家）" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（15家）" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（19条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -851,17 +851,17 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1456</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8371</v>
+        <v>8370</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>8383</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
     </row>
@@ -9951,14 +9951,14 @@
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C431" s="2" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="D431" s="2" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E431" s="2" t="n">
         <v>0</v>
@@ -9972,14 +9972,14 @@
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C432" s="2" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D432" s="2" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E432" s="2" t="n">
         <v>0</v>
@@ -9993,14 +9993,14 @@
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C433" s="2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D433" s="2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E433" s="2" t="n">
         <v>0</v>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C434" s="2" t="n">
@@ -10035,38 +10035,38 @@
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C435" s="2" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="D435" s="2" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="E435" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="2" t="inlineStr">
+      <c r="A436" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B436" s="2" t="inlineStr">
-        <is>
-          <t>青海</t>
-        </is>
-      </c>
-      <c r="C436" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D436" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E436" s="2" t="n">
-        <v>0</v>
+      <c r="B436" s="3" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="C436" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D436" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E436" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -10080,13 +10080,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
   </cols>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>小米汽车北京朝阳区东坝万达</t>
+          <t>小米汽车北京市大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -10274,12 +10274,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>东坝万达广场一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京朝阳区东坝万达</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>东坝万达广场一层中庭</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市花都区建设北路</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市花都区建设北路223号</t>
+          <t>龙溪大道502号自编1</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>小米汽车广东省广州市花都区建设北路</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>龙溪大道502号自编1</t>
+          <t>广东省广州市花都区建设北路223号</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -10982,6 +10982,38 @@
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>【测试】HIMA授权交付中心</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>阿里地区</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>官方将安排优质的门店尽快与您联系</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>全新</t>
         </is>
@@ -11401,7 +11433,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -11416,12 +11448,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>深圳市福田区</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>连续在档 5 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
+          <t>连续在档 4 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11465,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -11448,12 +11480,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>深圳市福田区</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>连续在档 4 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
+          <t>连续在档 5 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
         </is>
       </c>
     </row>
@@ -11583,17 +11615,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11603,7 +11635,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
+          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
@@ -11615,17 +11647,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11635,7 +11667,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
+          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11679,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11667,7 +11699,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
+          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11711,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11699,29 +11731,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11731,7 +11763,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
+          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11775,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11763,7 +11795,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
+          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11807,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11795,7 +11827,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
+          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -11807,17 +11839,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11827,7 +11859,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
+          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11871,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11859,7 +11891,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
+          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11903,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11891,7 +11923,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
+          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11935,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11923,7 +11955,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
         </is>
       </c>
     </row>
@@ -11962,22 +11994,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11987,7 +12019,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
+          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12063,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>华为授权体验店（融侨外滩壹号）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>华为授权体验店（融侨外滩）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12058,22 +12090,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融侨外滩壹号）</t>
+          <t>济南济西保时捷中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融侨外滩）</t>
+          <t>济南保时捷中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12090,22 +12122,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>济南济西保时捷中心</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>济南保时捷中心</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
